--- a/lead_generation_forms/007_e_commerce_chat_integration_registration--lead_generation_forms.xlsx
+++ b/lead_generation_forms/007_e_commerce_chat_integration_registration--lead_generation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Online Store Info</t>
+          <t>1. What is the name of your online store?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,7 +538,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Platform Info</t>
+          <t>2. Which platform are you using for your e-commerce integration?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,24 +561,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>chat_feature_p</t>
+          <t>payment_info</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chat Feature</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Select a chat feature</t>
-        </is>
-      </c>
+          <t>3. What is the payment info for your e-commerce store?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -598,14 +594,10 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chat Feature</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Select one or more chat features</t>
-        </is>
-      </c>
+          <t>4. Which features do you have integrated in your chat?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -625,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Integration Preferences</t>
+          <t>5. What are your integration preferences?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -643,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>integration_preferences</t>
+          <t>other_questions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Integration Preferences</t>
+          <t>6. Do you have any other questions about our e-commerce chat integration?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -666,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>payment_info</t>
+          <t>message</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Payment Info</t>
+          <t>7. Would you like to share a message with us about your e-commerce store?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -689,16 +681,108 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>payment_info</t>
+          <t>feedback</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Payment Info</t>
+          <t>8. Do you have any feedback about our e-commerce chat integration?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>schedule_call</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>9. Would you like to schedule a call back with us about your e-commerce chat integration?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>additional_info</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>10. Is there anything else we should know about your e-commerce store?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>terms_agreement</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>11. Do you confirm that you have read and agree to our terms and conditions?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>confirm_terms_agreement</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>12. Confirm</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -715,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -743,51 +827,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>chat_feature_p_choices</t>
+          <t>platform_info_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>shopify</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Shopify</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>chat_feature_p_choices</t>
+          <t>platform_info_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>woocommerce</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>WooCommerce</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>chat_feature_p_choices</t>
+          <t>platform_info_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>bigcommerce</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>BigCommerce</t>
         </is>
       </c>
     </row>
@@ -799,10 +883,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>chat_feature_p_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
